--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/tester-perf-medium.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/tester-perf-medium.xlsx
@@ -460,19 +460,19 @@
         <v>Latency (độ trễ mạng) đo lường thời gian gói tin đi trên đường truyền. Response Time = Latency (request) + Server Processing Time + Latency (response) + Client Rendering (nếu có).</v>
       </c>
       <c r="F2" t="str">
+        <v>Latency đo lường bằng số lượng pixels hiển thị; còn Response Time đo lường bằng giây — đơn vị đo lường</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Latency luôn luôn có giá trị lớn gấp đôi so với Response Time trong mọi điều kiện mạng — so sánh quy mô giá trị</v>
+      </c>
+      <c r="H2" t="str">
         <v>Latency là thời gian truyền gói tin từ client đến server; Response Time bao gồm cả Latency và thời gian server xử lý yêu cầu đó — thời gian truyền dẫn mạng vs tổng thời gian xử lý</v>
       </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
         <v>Latency chỉ áp dụng cho kiểm thử tự động; còn Response Time chỉ áp dụng cho kiểm thử thủ công — phân loại phương pháp test</v>
       </c>
-      <c r="H2" t="str">
-        <v>Latency đo lường bằng số lượng pixels hiển thị; còn Response Time đo lường bằng giây — đơn vị đo lường</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Latency luôn luôn có giá trị lớn gấp đôi so với Response Time trong mọi điều kiện mạng — so sánh quy mô giá trị</v>
-      </c>
       <c r="J2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -495,13 +495,13 @@
         <v>Duy trì tải lượng người dùng dự kiến trong một khoảng thời gian dài (24-72 giờ) để phát hiện các lỗi rò rỉ bộ nhớ (Memory Leaks) hoặc đầy ổ cứng log — kiểm thử độ bền phát hiện rò rỉ</v>
       </c>
       <c r="G3" t="str">
+        <v>Đo lường thời gian cần thiết để khôi phục hệ thống máy chủ sau khi bị cháy nổ — phục vụ diễn tập cháy nổ</v>
+      </c>
+      <c r="H3" t="str">
         <v>Tăng tải đột biến lên gấp 10 lần trong vòng 5 giây rồi ngắt tải ngay lập tức — kiểm thử đột biến tải</v>
       </c>
-      <c r="H3" t="str">
+      <c r="I3" t="str">
         <v>Kiểm tra khả năng chịu va đập vật lý của các thiết bị điện thoại di động thông minh — kiểm tra độ bền điện thoại</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Đo lường thời gian cần thiết để khôi phục hệ thống máy chủ sau khi bị cháy nổ — phục vụ diễn tập cháy nổ</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -524,19 +524,19 @@
         <v>WHERE lọc các dòng thô ở tầng vật lý (giảm số lượng dòng đưa vào xử lý). HAVING lọc trên tập kết quả đã được GROUP BY và tính toán hàm tổng hợp (như SUM, AVG), do đó sử dụng HAVING sai cách trên bảng lớn sẽ gây chậm truy vấn.</v>
       </c>
       <c r="F4" t="str">
-        <v>WHERE lọc dữ liệu trước khi thực hiện gom nhóm (GROUP BY) và chạy nhanh hơn; HAVING chỉ lọc dữ liệu sau khi đã gom nhóm xong các hàm tổng hợp — lọc trước khi nhóm vs lọc sau khi nhóm</v>
+        <v>WHERE do QA tự viết; còn HAVING do lập trình viên tự động chèn vào code — phân chia vai trò viết câu lệnh</v>
       </c>
       <c r="G4" t="str">
         <v>WHERE chỉ dùng cho kiểu dữ liệu số; còn HAVING chỉ dùng cho kiểu dữ liệu chuỗi văn bản — kiểu dữ liệu lọc</v>
       </c>
       <c r="H4" t="str">
-        <v>WHERE do QA tự viết; còn HAVING do lập trình viên tự động chèn vào code — phân chia vai trò viết câu lệnh</v>
+        <v>WHERE lọc dữ liệu trước khi thực hiện gom nhóm (GROUP BY) và chạy nhanh hơn; HAVING chỉ lọc dữ liệu sau khi đã gom nhóm xong các hàm tổng hợp — lọc trước khi nhóm vs lọc sau khi nhóm</v>
       </c>
       <c r="I4" t="str">
         <v>WHERE bắt buộc phải đi kèm với từ khóa ORDER BY; còn HAVING đi kèm với DISTINCT — liên kết từ khóa</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -559,13 +559,13 @@
         <v>Vì chế độ GUI tiêu tốn rất nhiều tài nguyên CPU/RAM của máy chạy test để vẽ biểu đồ thời gian thực, dẫn đến kết quả đo lường tải bị sai lệch hoặc sập tool — chế độ Non-GUI tiết kiệm tài nguyên máy chạy test</v>
       </c>
       <c r="G5" t="str">
+        <v>Vì chế độ GUI chỉ hỗ trợ chạy tối đa 10 người dùng ảo trong toàn bộ phiên chạy — giới hạn người dùng GUI</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Vì chế độ Non-GUI bắt buộc phải có chứng chỉ kỹ sư mạng Cisco mới vận hành được — yêu cầu chứng chỉ mạng</v>
+      </c>
+      <c r="I5" t="str">
         <v>Vì chế độ Non-GUI tự động mã hóa toàn bộ dữ liệu báo cáo gửi đi bằng giao thức bảo mật HTTPS — bảo mật báo cáo</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Vì chế độ GUI chỉ hỗ trợ chạy tối đa 10 người dùng ảo trong toàn bộ phiên chạy — giới hạn người dùng GUI</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Vì chế độ Non-GUI bắt buộc phải có chứng chỉ kỹ sư mạng Cisco mới vận hành được — yêu cầu chứng chỉ mạng</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -588,10 +588,10 @@
         <v>UNION thực hiện thêm một bước lọc trùng (sorting and filtering) ngầm nên tiêu tốn tài nguyên CPU của database hơn. Nếu nghiệp vụ chắc chắn không có trùng lặp hoặc chấp nhận trùng lặp, nên dùng `UNION ALL` để tối ưu hiệu năng.</v>
       </c>
       <c r="F6" t="str">
+        <v>UNION chỉ ghép các cột theo chiều dọc; còn UNION ALL ghép các cột theo chiều ngang — hướng ghép bảng</v>
+      </c>
+      <c r="G6" t="str">
         <v>UNION gộp kết quả và tự động loại bỏ các dòng trùng lặp (chạy chậm hơn do phải lọc); UNION ALL gộp toàn bộ bao gồm cả dòng trùng lặp (chạy nhanh hơn) — loại bỏ trùng lặp vs gộp toàn bộ</v>
-      </c>
-      <c r="G6" t="str">
-        <v>UNION chỉ ghép các cột theo chiều dọc; còn UNION ALL ghép các cột theo chiều ngang — hướng ghép bảng</v>
       </c>
       <c r="H6" t="str">
         <v>UNION chỉ chạy trên hệ quản trị MySQL; còn UNION ALL chỉ chạy trên Microsoft SQL Server — hệ quản trị cơ sở dữ liệu hỗ trợ</v>
@@ -600,7 +600,7 @@
         <v>UNION bắt buộc phải có tối thiểu 3 bảng dữ liệu tham gia liên kết — số lượng bảng tối thiểu</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -623,13 +623,13 @@
         <v>Atomicity (Tính nguyên tố), Consistency (Tính nhất quán), Isolation (Tính cô lập), Durability (Tính bền vững) — tiêu chuẩn giao dịch ACID</v>
       </c>
       <c r="G7" t="str">
+        <v>Authentication, Cryptography, Integrity, Decryption — quy chuẩn bảo mật dữ liệu</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Aggregation, Collection, Indexing, De-duplication — quy trình xử lý dữ liệu lớn</v>
+      </c>
+      <c r="I7" t="str">
         <v>Accuracy, Compatibility, Integration, Development — quy chuẩn chất lượng phần mềm</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Authentication, Cryptography, Integrity, Decryption — quy chuẩn bảo mật dữ liệu</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Aggregation, Collection, Indexing, De-duplication — quy trình xử lý dữ liệu lớn</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -652,19 +652,19 @@
         <v>Nếu không có Assertion, JMeter chỉ kiểm tra lỗi ở tầng mạng (ví dụ kết nối được là đánh dấu Pass). Nhưng máy chủ có thể trả về trang lỗi 500 kèm nội dung "Database Error" dạng HTML. Dùng Response Assertion để kiểm tra sự hiện diện của text đúng hoặc status code 200.</v>
       </c>
       <c r="F8" t="str">
-        <v>Kiểm tra dữ liệu phản hồi (Status Code, Text trong body) của máy chủ trả về có đúng kỳ vọng không, nếu sai sẽ đánh dấu request đó bị lỗi (Fail) — xác thực phản hồi máy chủ</v>
+        <v>Mã hóa toàn bộ nội dung của các file báo cáo kết quả chạy test sang định dạng PDF — định dạng báo cáo</v>
       </c>
       <c r="G8" t="str">
         <v>Tự động điều chỉnh tần suất gửi yêu cầu API của người dùng ảo tăng lên gấp đôi — tăng tần suất gửi</v>
       </c>
       <c r="H8" t="str">
-        <v>Mã hóa toàn bộ nội dung của các file báo cáo kết quả chạy test sang định dạng PDF — định dạng báo cáo</v>
+        <v>Kiểm tra dữ liệu phản hồi (Status Code, Text trong body) của máy chủ trả về có đúng kỳ vọng không, nếu sai sẽ đánh dấu request đó bị lỗi (Fail) — xác thực phản hồi máy chủ</v>
       </c>
       <c r="I8" t="str">
         <v>Tự động chèn các mã số định danh ID ngẫu nhiên vào database khi nhận được request — chèn dữ liệu ID</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -684,19 +684,19 @@
         <v>Index giống như mục lục của cuốn sách. Tra cứu từ khóa trong mục lục giúp lật nhanh đến trang cần tìm (quét chỉ mục nhanh hơn quét toàn bảng Table Scan). Tuy nhiên, mỗi khi thêm/sửa/xóa dòng, database phải cập nhật lại mục lục này nên làm chậm tốc độ ghi.</v>
       </c>
       <c r="F9" t="str">
-        <v>Giúp tăng tốc độ truy vấn đọc dữ liệu (SELECT) cực nhanh; nhưng làm chậm tốc độ ghi dữ liệu (INSERT/UPDATE/DELETE) và tiêu tốn dung lượng ổ cứng để lưu trữ index — tăng tốc độ đọc vs giảm tốc độ ghi</v>
+        <v>Giúp bảo mật dữ liệu tuyệt đối trước hacker; nhưng làm tăng giá tiền mua bản quyền phần mềm cơ sở dữ liệu — bảo mật vs chi phí</v>
       </c>
       <c r="G9" t="str">
-        <v>Giúp bảo mật dữ liệu tuyệt đối trước hacker; nhưng làm tăng giá tiền mua bản quyền phần mềm cơ sở dữ liệu — bảo mật vs chi phí</v>
+        <v>Giúp loại bỏ hoàn toàn việc phải viết các câu lệnh JOIN phức tạp giữa các bảng liên kết — loại bỏ JOIN</v>
       </c>
       <c r="H9" t="str">
         <v>Giúp tự động sửa các lỗi chính tả trong bảng; nhưng giới hạn số lượng cột tối đa của bảng dưới 10 cột — sửa chính tả vs giới hạn cột</v>
       </c>
       <c r="I9" t="str">
-        <v>Giúp loại bỏ hoàn toàn việc phải viết các câu lệnh JOIN phức tạp giữa các bảng liên kết — loại bỏ JOIN</v>
+        <v>Giúp tăng tốc độ truy vấn đọc dữ liệu (SELECT) cực nhanh; nhưng làm chậm tốc độ ghi dữ liệu (INSERT/UPDATE/DELETE) và tiêu tốn dung lượng ổ cứng để lưu trữ index — tăng tốc độ đọc vs giảm tốc độ ghi</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -716,19 +716,19 @@
         <v>Memory Leak thường do lỗi lập trình (quên đóng kết nối, quên giải phóng con trỏ). Lỗi này chỉ có thể phát hiện hiệu quả thông qua việc chạy Soak testing (Endurance testing) trong thời gian dài để quan sát đồ thị RAM tiêu thụ đi lên tuyến tính.</v>
       </c>
       <c r="F10" t="str">
+        <v>Hệ thống tự động nén kích thước của các tệp tin lưu trữ để giải phóng không gian ổ cứng — tự động nén giải phóng ổ cứng</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Lập trình viên quên không lắp card màn hình vào bo mạch chủ của máy tính chạy phần mềm — thiếu card màn hình</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Dữ liệu trong bộ nhớ RAM bị hacker lấy trộm và công bố công khai ra internet — rò rỉ dữ liệu</v>
+      </c>
+      <c r="I10" t="str">
         <v>Ứng dụng chiếm dụng bộ nhớ RAM nhưng không giải phóng sau khi sử dụng xong, làm dung lượng RAM trống giảm dần theo thời gian dẫn đến sập hệ thống — rò rỉ RAM gây sập máy chủ</v>
       </c>
-      <c r="G10" t="str">
-        <v>Dữ liệu trong bộ nhớ RAM bị hacker lấy trộm và công bố công khai ra internet — rò rỉ dữ liệu</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Hệ thống tự động nén kích thước của các tệp tin lưu trữ để giải phóng không gian ổ cứng — tự động nén giải phóng ổ cứng</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Lập trình viên quên không lắp card màn hình vào bo mạch chủ của máy tính chạy phần mềm — thiếu card màn hình</v>
-      </c>
       <c r="J10">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -748,7 +748,7 @@
         <v>Toàn vẹn tham chiếu ngăn chặn hiện tượng "mồ côi" dữ liệu. Ví dụ: không được phép tạo đơn hàng có `customer_id = 99` nếu trong bảng Customer không tồn tại khách hàng có ID = 99.</v>
       </c>
       <c r="F11" t="str">
-        <v>Đảm bảo mọi giá trị khóa ngoại trong bảng con phải luôn tồn tại khóa chính tương ứng trong bảng cha — toàn vẹn khóa ngoại</v>
+        <v>Xác nhận rằng mật khẩu của admin đã được mã hóa bằng thuật toán MD5 — mã hóa mật khẩu</v>
       </c>
       <c r="G11" t="str">
         <v>Kiểm tra xem tên của các cột dữ liệu có được viết đúng chính tả tiếng Anh chuyên ngành hay không — chính tả tên cột</v>
@@ -757,10 +757,10 @@
         <v>Đảm bảo dữ liệu số trong bảng không bao giờ vượt quá 10 chữ số tự nhiên — giới hạn chữ số</v>
       </c>
       <c r="I11" t="str">
-        <v>Xác nhận rằng mật khẩu của admin đã được mã hóa bằng thuật toán MD5 — mã hóa mật khẩu</v>
+        <v>Đảm bảo mọi giá trị khóa ngoại trong bảng con phải luôn tồn tại khóa chính tương ứng trong bảng cha — toàn vẹn khóa ngoại</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
